--- a/erace-rx-v2/BOM.xlsx
+++ b/erace-rx-v2/BOM.xlsx
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="113">
-  <si>
-    <t xml:space="preserve">Comment</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="115">
   <si>
     <t xml:space="preserve">Designator</t>
   </si>
@@ -73,331 +70,340 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Comment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C293767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANT3216LL00R2400A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AE2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C152351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0479480001 2.4GHz Molex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C318884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TS-1187A-B-A-B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1,C4,C6,C10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C52923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1uF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">470nF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C19,C21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C72135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2,C3,C11,C12,C13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C307331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 nF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C20,C26,C27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C45783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22uF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C5,C14,C16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C15195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10nF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C7,C8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C19702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10uF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C965794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D2,D4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOD-323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C191023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1N5819WS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0402-4P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C6054595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4GHz Filter RF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMD,P=1mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C5340778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0mm-8P-WT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C393939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TYPE-C16PIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C880712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0nH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C19898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0nH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C57838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15µH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1,P2,P3,P4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">do not populate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solder Pad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1,Q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOT-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C8545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2N7002 MOSFET Jiangsu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R1,R2,R3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C25744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 Ohm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R4,R6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C11702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R5,R7,R11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C25890</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R8,R12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C25105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33 Ohm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R9,R10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C25905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QFN-24-EP(4x4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2151551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SX1281IMLTRT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QFN-32-EP(5x5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2858491</t>
+  </si>
+  <si>
     <t xml:space="preserve">ESP32-C3FH4</t>
   </si>
   <si>
-    <t xml:space="preserve">U1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QFN-32-EP(5x5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2858491</t>
+    <t xml:space="preserve">U2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOT-223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C6186</t>
   </si>
   <si>
     <t xml:space="preserve">AMS1117-3.3</t>
   </si>
   <si>
-    <t xml:space="preserve">U2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOT-223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C6186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SX1281IMLTRT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QFN-24-EP(4x4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2151551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TS-1187A-B-A-B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C318884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0mm-8P-WT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMD,P=1mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C5340778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANT3216LL00R2400A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C293767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TYPE-C16PIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C393939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0479480001 2.4GHz Molex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AE2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C3285490</t>
-  </si>
-  <si>
-    <t xml:space="preserve">do not populate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4GHz Filter RF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0402-4P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2650940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2N7002 MOSFET Jiangsu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q1,Q2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOT-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C8545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LED green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D1,D3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C965794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1N5819WS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2,D4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOD-323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C191023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solder Pad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P1,P2,P3,P4</t>
+    <t xml:space="preserve">Y1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMD3225-4P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C331597</t>
   </si>
   <si>
     <t xml:space="preserve">40MHz Crystal</t>
   </si>
   <si>
-    <t xml:space="preserve">Y1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMD3225-4P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C331597</t>
+    <t xml:space="preserve">Y2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C7294606</t>
   </si>
   <si>
     <t xml:space="preserve">52MHz Crystal</t>
   </si>
   <si>
-    <t xml:space="preserve">Y2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C7294606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12pF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C7,C8,C17,C18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C1547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 Ohm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0nH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C880712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15µH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C57838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R5,R7,R11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C25890</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R4,R6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C11702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R9,R10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C25905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R1,R2,R3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C25744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33 Ohm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R8,R12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C25105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100 nF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2,C3,C11,C12,C13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C307331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1uF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C1,C4,C6,C10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C52923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10nF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C5,C14,C16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C15195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">470nF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C1623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10uF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C19702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22uF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C20,C26,C27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C45783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0nH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C19898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2pF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C19,C21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C72135</t>
+    <t xml:space="preserve">D3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C25503345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED red</t>
   </si>
 </sst>
 </file>
@@ -407,7 +413,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -457,6 +463,14 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -509,17 +523,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -536,6 +550,14 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -790,11 +812,12 @@
   <dimension ref="A1:E34"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="20" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="22.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="22.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="24.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="13.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="26.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="10.41"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -804,13 +827,13 @@
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3"/>
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3"/>
     </row>
     <row r="2" s="6" customFormat="true" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
@@ -822,10 +845,10 @@
       <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="5"/>
+      <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="5"/>
     </row>
     <row r="3" s="6" customFormat="true" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
@@ -834,397 +857,399 @@
       <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="5"/>
     </row>
     <row r="4" s="6" customFormat="true" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5"/>
+      <c r="E4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="5"/>
     </row>
     <row r="5" s="6" customFormat="true" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5"/>
+      <c r="E5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="5"/>
     </row>
     <row r="6" s="6" customFormat="true" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5"/>
+      <c r="E6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="5"/>
     </row>
     <row r="7" s="6" customFormat="true" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="D7" s="5"/>
+      <c r="E7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="5"/>
     </row>
     <row r="8" s="6" customFormat="true" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="D9" s="5"/>
+      <c r="E9" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="5"/>
+        <v>37</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="5"/>
+        <v>40</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="5"/>
+        <v>46</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="5"/>
+        <v>58</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="5"/>
+        <v>16</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="5" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="5" t="s">
+      <c r="B20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="5"/>
-    </row>
-    <row r="20" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="5"/>
+      <c r="E22" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B23" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="5"/>
+      <c r="E23" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="D25" s="5"/>
+      <c r="E25" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="D26" s="5"/>
+      <c r="E26" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="D28" s="5"/>
+      <c r="E28" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="5"/>
+      <c r="E29" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
@@ -1234,72 +1259,71 @@
         <v>98</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D30" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E31" s="5"/>
+        <v>103</v>
+      </c>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E32" s="5"/>
+        <v>107</v>
+      </c>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="20" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E33" s="5"/>
+        <v>110</v>
+      </c>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="20" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D34" s="5" t="s">
+      <c r="A34" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E34" s="5"/>
+      <c r="B34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>114</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
